--- a/02-精益培训/03-培训计划/02-季度培训计划模板.xlsx
+++ b/02-精益培训/03-培训计划/02-季度培训计划模板.xlsx
@@ -89,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -116,11 +116,20 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="001F3A5F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -144,6 +153,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,7 +537,13 @@
           <t>02-季度培训计划模板</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -535,6 +551,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -542,6 +559,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -549,6 +567,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
@@ -556,6 +575,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -563,6 +583,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -570,6 +591,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
@@ -577,6 +599,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -584,6 +607,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
@@ -591,6 +615,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
@@ -598,6 +623,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
@@ -605,6 +631,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
@@ -612,6 +639,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
@@ -647,6 +675,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
@@ -654,6 +683,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
@@ -867,7 +897,7 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>三楼培训室 / 冷镦车间</t>
+          <t>三楼培训室 / 机加工车间</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1201,7 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>冷镦车间</t>
+          <t>机加工车间</t>
         </is>
       </c>
       <c r="H4" s="9" t="inlineStr">
@@ -1627,7 +1657,7 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>冷镦车间</t>
+          <t>机加工车间</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
